--- a/data/trans_dic/IP44C$ninguna_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que no han tenido retrasos en pagos</t>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,43; 94,9</t>
+          <t>84,81; 94,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,32; 94,91</t>
+          <t>85,28; 94,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,94; 93,88</t>
+          <t>87,37; 93,84</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,48; 91,87</t>
+          <t>79,42; 91,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,55; 92,66</t>
+          <t>80,34; 92,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,48; 90,89</t>
+          <t>82,35; 90,96</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,09; 91,61</t>
+          <t>72,84; 91,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,69; 93,46</t>
+          <t>74,18; 93,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,09; 91,0</t>
+          <t>77,75; 90,05</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,18; 88,36</t>
+          <t>47,21; 88,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,54; 91,59</t>
+          <t>83,46; 91,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,55; 88,89</t>
+          <t>63,82; 88,63</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,2; 82,07</t>
+          <t>65,64; 82,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,95; 83,98</t>
+          <t>72,33; 84,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,47; 81,56</t>
+          <t>72,28; 82,05</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,86; 87,71</t>
+          <t>71,82; 87,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,24; 84,21</t>
+          <t>65,5; 84,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,81; 84,36</t>
+          <t>71,82; 84,03</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,18; 85,79</t>
+          <t>67,31; 85,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,94; 87,67</t>
+          <t>82,52; 87,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,91; 85,77</t>
+          <t>76,42; 85,71</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>93578</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121856</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>215433</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>87248; 97585</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>114140; 126772</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>206822; 222146</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>81963</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83722</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>165685</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>75192; 86923</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>76786; 88057</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156677; 173046</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>43473</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55200</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98673</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>37773; 47286</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47368; 59480</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>89971; 104198</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>164306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187214</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>351520</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>101153; 190463</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177482; 194712</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>272443; 378364</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>86606</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>122698</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>209305</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>75180; 94364</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>113474; 132945</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>196186; 222702</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>53685</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52109</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>105794</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>47724; 58451</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>45118; 58295</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>97194; 113726</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>523611</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>622798</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1146409</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>433890; 551885</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>603778; 640488</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1051839; 1179644</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$ninguna_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,81; 94,85</t>
+          <t>85,11; 95,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,28; 94,72</t>
+          <t>85,15; 94,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,37; 93,84</t>
+          <t>87,08; 93,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,42; 91,81</t>
+          <t>79,47; 91,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,34; 92,14</t>
+          <t>81,37; 92,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,35; 90,96</t>
+          <t>82,29; 90,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,84; 91,18</t>
+          <t>72,8; 91,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,18; 93,15</t>
+          <t>76,1; 93,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,75; 90,05</t>
+          <t>78,1; 90,69</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,21; 88,89</t>
+          <t>47,11; 89,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,46; 91,57</t>
+          <t>83,7; 91,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,82; 88,63</t>
+          <t>65,89; 88,87</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,64; 82,39</t>
+          <t>66,93; 82,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,33; 84,74</t>
+          <t>70,75; 84,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,28; 82,05</t>
+          <t>72,27; 82,22</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,82; 87,97</t>
+          <t>71,8; 87,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,5; 84,62</t>
+          <t>65,23; 84,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,82; 84,03</t>
+          <t>71,4; 83,93</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>67,31; 85,61</t>
+          <t>69,58; 85,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,52; 87,54</t>
+          <t>82,48; 87,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76,42; 85,71</t>
+          <t>77,06; 85,51</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87248; 97585</t>
+          <t>87558; 97794</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114140; 126772</t>
+          <t>113971; 127038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206822; 222146</t>
+          <t>206140; 222072</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75192; 86923</t>
+          <t>75240; 87084</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76786; 88057</t>
+          <t>77770; 88408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>156677; 173046</t>
+          <t>156557; 173043</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37773; 47286</t>
+          <t>37755; 47580</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47368; 59480</t>
+          <t>48592; 59500</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89971; 104198</t>
+          <t>90369; 104944</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>101153; 190463</t>
+          <t>100930; 190963</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177482; 194712</t>
+          <t>177982; 194164</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>272443; 378364</t>
+          <t>281298; 379400</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75180; 94364</t>
+          <t>76653; 94076</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>113474; 132945</t>
+          <t>111003; 131942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196186; 222702</t>
+          <t>196160; 223143</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47724; 58451</t>
+          <t>47711; 58430</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45118; 58295</t>
+          <t>44935; 58257</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97194; 113726</t>
+          <t>96629; 113585</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>433890; 551885</t>
+          <t>448528; 552211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>603778; 640488</t>
+          <t>603472; 638600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1051839; 1179644</t>
+          <t>1060658; 1176899</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,11; 95,06</t>
+          <t>84,44; 94,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,15; 94,92</t>
+          <t>84,68; 94,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,08; 93,81</t>
+          <t>86,11; 93,31</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,47; 91,98</t>
+          <t>81,49; 92,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,37; 92,5</t>
+          <t>78,59; 91,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,29; 90,95</t>
+          <t>82,11; 90,79</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,8; 91,75</t>
+          <t>76,49; 93,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,1; 93,18</t>
+          <t>72,94; 91,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,1; 90,69</t>
+          <t>78,23; 90,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,11; 89,13</t>
+          <t>82,95; 91,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,7; 91,31</t>
+          <t>79,79; 89,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,89; 88,87</t>
+          <t>83,03; 89,76</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,93; 82,14</t>
+          <t>69,95; 83,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,75; 84,1</t>
+          <t>71,11; 84,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,27; 82,22</t>
+          <t>72,06; 81,68</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,8; 87,93</t>
+          <t>63,86; 83,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,23; 84,57</t>
+          <t>71,25; 87,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,4; 83,93</t>
+          <t>70,94; 83,62</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>69,58; 85,66</t>
+          <t>82,39; 87,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,48; 87,28</t>
+          <t>81,64; 86,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,06; 85,51</t>
+          <t>82,73; 86,3</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>140</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93578</t>
+          <t>108098</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>121856</t>
+          <t>91690</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215433</t>
+          <t>199788</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87558; 97794</t>
+          <t>100981; 113218</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113971; 127038</t>
+          <t>85844; 96003</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206140; 222072</t>
+          <t>190273; 206186</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81963</t>
+          <t>80302</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83722</t>
+          <t>83063</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165685</t>
+          <t>163365</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75240; 87084</t>
+          <t>74484; 84934</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77770; 88408</t>
+          <t>75879; 88363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>156557; 173043</t>
+          <t>154327; 170642</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55200</t>
+          <t>44664</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98673</t>
+          <t>94111</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37755; 47580</t>
+          <t>43553; 53377</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48592; 59500</t>
+          <t>39008; 48989</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90369; 104944</t>
+          <t>86384; 100283</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>236</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>164306</t>
+          <t>172537</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>187214</t>
+          <t>150908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351520</t>
+          <t>323445</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100930; 190963</t>
+          <t>163087; 179984</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177982; 194164</t>
+          <t>140406; 158119</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>281298; 379400</t>
+          <t>309342; 334418</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>132</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86606</t>
+          <t>109685</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>122698</t>
+          <t>88465</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209305</t>
+          <t>198150</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76653; 94076</t>
+          <t>99295; 118239</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111003; 131942</t>
+          <t>81050; 95748</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196160; 223143</t>
+          <t>184436; 209046</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>75</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52109</t>
+          <t>54818</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105794</t>
+          <t>103471</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47711; 58430</t>
+          <t>41815; 54697</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44935; 58257</t>
+          <t>48483; 59585</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96629; 113585</t>
+          <t>94722; 111658</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>523611</t>
+          <t>568720</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>622798</t>
+          <t>513608</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1146409</t>
+          <t>1082328</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>448528; 552211</t>
+          <t>553633; 586042</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>603472; 638600</t>
+          <t>497544; 529440</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1060658; 1176899</t>
+          <t>1060056; 1105872</t>
         </is>
       </c>
     </row>
